--- a/data/instance_P5_M8_T6.xlsx
+++ b/data/instance_P5_M8_T6.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Custos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demanda_Cor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Estoque_Cor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="De_Para_Cores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +23,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,52 +428,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -497,7 +492,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>69.96069176347025</v>
+        <v>69.96069176347024</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -613,7 +608,7 @@
         <v>23.49816450134396</v>
       </c>
       <c r="F7" t="n">
-        <v>36.8830335213198</v>
+        <v>36.88303352131979</v>
       </c>
       <c r="G7" t="n">
         <v>37.61562546600102</v>
@@ -641,42 +636,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01/2024</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>02/2024</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>03/2024</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>04/2024</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>05/2024</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>06/2024</t>
         </is>
@@ -784,16 +779,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28906.25195144572</v>
+        <v>28906.25195144573</v>
       </c>
       <c r="D6" t="n">
         <v>36184.22930662797</v>
       </c>
       <c r="E6" t="n">
-        <v>53473.97997910193</v>
+        <v>53473.97997910195</v>
       </c>
       <c r="F6" t="n">
-        <v>41841.68113571377</v>
+        <v>41841.68113571376</v>
       </c>
       <c r="G6" t="n">
         <v>45770.06976121849</v>
@@ -847,17 +842,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>12/2023</t>
         </is>
@@ -953,17 +948,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CUSTO_UNITARIO</t>
         </is>
@@ -1011,7 +1006,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.589349362259787</v>
+        <v>9.589349362259789</v>
       </c>
     </row>
     <row r="5">
@@ -1059,47 +1054,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1290,6 +1285,2302 @@
       <c r="I7" t="n">
         <v>1</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PRAZO_ENTREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13486.73570870861</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>24844.34923503695</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5890.141543483896</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12932.1260442171</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45326</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23822.68495011615</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5647.923597214683</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16480.8283626157</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45355</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30359.86352569619</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7197.769267991803</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45359</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13520.07353654695</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45402</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>24905.76191898379</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>45404</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5904.701369446333</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>45404</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14004.73912787729</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>25798.57997913464</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>45436</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6116.372228566722</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12732.54316606093</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>45447</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>23455.02691682022</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>45462</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5560.758590990332</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>45471</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>21647.94742077701</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2684.660574013124</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5570.855436629193</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>35907.77801188202</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4453.087124389131</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9240.462223350463</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>45339</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>32480.12087601605</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4028.007748731454</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>45363</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8358.393266923074</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>45361</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>37081.31590834705</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>45407</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4598.622904826502</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>45396</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9542.458982837141</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>45407</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>39291.79488872345</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4872.754472727744</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10111.30085066085</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>45419</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>35643.12252130657</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4420.26599139977</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>9172.356113803517</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>45452</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>6708.577115404939</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>45311</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>37825.46473554843</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6674.659462420605</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>37634.22433317974</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>45330</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>6827.438812995094</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>38495.65140453367</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45381</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7574.157083724603</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>45388</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>42705.92805947585</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>45387</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4941.7731375385</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45429</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>27863.5636632702</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>45414</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4838.16058891828</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>45452</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>27279.35739470175</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>45457</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11910.71458964081</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>16995.53736180491</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14909.57833763043</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>21274.65096899754</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>45348</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22033.75638505758</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>45354</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>31440.22359404436</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>45375</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>17240.7105146442</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>45408</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>24600.97062106955</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>45409</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>18859.38857066377</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>45419</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>26910.68119055471</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>45440</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>23463.5596369241</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>45447</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>33480.42650582115</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>45459</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12387.2619404761</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>19582.67471031772</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>4533.201384782209</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>17600.68271752463</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>27824.42528405503</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>45332</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6441.087598824794</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13665.33354545847</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>45364</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>21603.14223713113</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>45363</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>5000.920239634669</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>45379</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>16626.47287393485</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>45385</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>26284.32428689513</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>6084.568988557973</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13610.2056118353</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>45424</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>21515.99203422252</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>45421</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>4980.745803488762</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>14298.20956631736</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>22603.63817465092</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5232.525453760197</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>45451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ESTOQUE_INICIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13859.5076576711</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25531.04442096466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6052.944432948962</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>33675.34660450869</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4176.233136014621</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8665.971145700707</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6260.794366833671</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>35300.69826511828</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18069.61800576015</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25783.74837371537</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14698.02770925778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>23235.69945454541</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5378.841578174767</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.7299264749367411</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>1.811843061256197</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.666107257361766</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1.251111779303514</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0.6827487569427967</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1.54139365346433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7996634774900864</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.573110694423703</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6965866273359699</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>1.096367290737411</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1.2328760680273</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.933434885570455</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.887212643968041</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1.450962667521628</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.949347868214772</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.899534832400317</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.201072402332937</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5267551759654816</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
